--- a/files/九龙-将军澳-LP10.xlsx
+++ b/files/九龙-将军澳-LP10.xlsx
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -10368,14 +10368,14 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
         <v>19947000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>16554</v>
+        <v>16540</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
       </c>
       <c r="G813" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="H813" s="5" t="n">
@@ -39456,7 +39456,7 @@
       </c>
       <c r="G845" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H845" s="5" t="n">
@@ -43866,10 +43866,10 @@
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>A | 1205呎 (4+房)
+          <t>A | 1206呎 (4+房)
 $1,995万
-$16,554/呎
-(已售)</t>
+$16,540/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
@@ -50071,7 +50071,7 @@
           <t>E | 488呎 (2房)
 $790万
 $16,193/呎
-(25年-03月)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">

--- a/files/九龙-将军澳-LP10.xlsx
+++ b/files/九龙-将军澳-LP10.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-B座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +145,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +226,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +656,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -41639,4 +41821,9031 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1-A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>53&amp;55</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3483呎 (4+房)
+$9300万
+$26,701/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 2653呎 (4+房)
+$6880万
+$25,933/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$4601万
+$21,500/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1949呎 (4+房)
+$4280万
+$21,960/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$4580万
+$21,402/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1949呎 (4+房)
+$4180万
+$21,447/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1202呎 (4+房)
+$2550万
+$21,215/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1532万
+$17,837/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1811万
+$19,667/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1065万
+$16,647/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$949万
+$17,130/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1202呎 (4+房)
+$2485万
+$20,674/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1532万
+$17,837/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1808万
+$19,628/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1065万
+$16,647/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$949万
+$17,099/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1202呎 (4+房)
+$2456万
+$20,428/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1526万
+$17,766/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1804万
+$19,588/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1062万
+$16,597/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$945万
+$17,063/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2446万
+$20,330/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1523万
+$17,730/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1800万
+$19,549/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1051万
+$16,417/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$909万
+$16,380/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2436万
+$20,249/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1577万
+$18,363/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1797万
+$19,510/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1049万
+$16,392/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$907万
+$16,377/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1202呎 (4+房)
+$2396万
+$19,938/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1584万
+$18,438/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1793万
+$19,471/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1038万
+$16,214/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$940万
+$16,930/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2357万
+$19,594/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1514万
+$17,625/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1790万
+$19,433/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1036万
+$16,191/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$938万
+$16,926/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2115万
+$17,583/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1496万
+$17,416/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1786万
+$19,394/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1025万
+$16,011/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$936万
+$16,894/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2108万
+$17,521/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1549万
+$18,036/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1783万
+$19,355/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1062万
+$16,594/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$934万
+$16,829/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2100万
+$17,460/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1556万
+$18,109/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1779万
+$19,316/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1050万
+$16,412/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$898万
+$16,184/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2100万
+$17,460/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1487万
+$17,311/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1776万
+$19,278/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1012万
+$15,816/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$932万
+$16,825/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1202呎 (4+房)
+$2164万
+$18,007/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1484万
+$17,277/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1772万
+$19,239/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1000万
+$15,622/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$928万
+$16,758/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1202呎 (4+房)
+$2079万
+$17,293/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1537万
+$17,892/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1768万
+$19,201/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$998万
+$15,602/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$927万
+$16,726/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2071万
+$17,218/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1478万
+$17,207/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1832万
+$19,886/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$995万
+$15,550/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$925万
+$16,661/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2064万
+$17,158/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 859呎 (3房)
+$1475万
+$17,173/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1761万
+$19,125/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$991万
+$15,484/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$889万
+$16,052/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1204呎 (4+房)
+$2371万
+$19,695/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1471万
+$17,140/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1758万
+$19,087/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$975万
+$15,236/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$921万
+$16,596/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1204呎 (4+房)
+$2378万
+$19,755/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1468万
+$17,105/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1754万
+$19,048/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1010万
+$15,780/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$919万
+$16,562/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2271万
+$18,881/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1465万
+$17,071/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1751万
+$19,010/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$971万
+$15,175/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$917万
+$16,560/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1204呎 (4+房)
+$2256万
+$18,741/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1462万
+$17,036/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1813万
+$19,687/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$969万
+$15,145/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$882万
+$15,897/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2256万
+$18,756/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1459万
+$17,002/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1744万
+$18,935/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$969万
+$15,145/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$916万
+$16,497/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1203呎 (4+房)
+$2028万
+$16,858/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1456万
+$16,969/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1740万
+$18,897/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1002万
+$15,653/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$912万
+$16,460/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1204呎 (4+房)
+$2022万
+$16,794/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1508万
+$17,573/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1802万
+$19,570/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$1000万
+$15,623/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$877万
+$15,802/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1204呎 (4+房)
+$2016万
+$16,743/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1514万
+$17,646/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1733万
+$18,821/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$998万
+$15,592/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$875万
+$15,771/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1204呎 (4+房)
+$2223万
+$18,463/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 858呎 (3房)
+$1502万
+$17,503/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1752万
+$19,020/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 640呎 (2房)
+$996万
+$15,561/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$906万
+$16,363/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$2245万
+$18,615/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1434万
+$16,734/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1740万
+$18,869/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$976万
+$15,397/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 541呎 (2房)
+$846万
+$15,641/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2155万
+$17,885/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1430万
+$16,684/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1810万
+$19,630/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$974万
+$15,366/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 541呎 (2房)
+$876万
+$16,200/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2202万
+$18,273/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1479万
+$17,261/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1729万
+$18,756/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$972万
+$15,336/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 541呎 (2房)
+$843万
+$15,580/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$2229万
+$18,482/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1421万
+$16,583/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1703万
+$18,488/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$972万
+$15,336/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 541呎 (2房)
+$875万
+$16,168/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$1972万
+$16,349/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1417万
+$16,533/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1772万
+$19,222/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$968万
+$15,274/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$871万
+$16,074/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$1966万
+$16,314/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1466万
+$17,106/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1756万
+$19,050/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$966万
+$15,244/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$869万
+$16,041/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2046万
+$16,981/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1408万
+$16,435/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1687万
+$18,302/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$964万
+$15,213/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$868万
+$16,009/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2126万
+$17,643/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1457万
+$17,004/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1682万
+$18,246/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$999万
+$15,756/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$866万
+$15,978/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2200万
+$18,256/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1453万
+$16,952/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1741万
+$18,879/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$997万
+$15,724/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$833万
+$15,365/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2194万
+$18,204/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1396万
+$16,287/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1693万
+$18,385/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$995万
+$15,692/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$862万
+$15,913/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2186万
+$18,144/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1392万
+$16,238/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1688万
+$18,330/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$993万
+$15,661/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$861万
+$15,882/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2107万
+$17,484/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1440万
+$16,800/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 921呎 (3房)
+$1662万
+$18,048/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$993万
+$15,661/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$830万
+$15,304/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2148万
+$17,825/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1383万
+$16,141/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1657万
+$17,974/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$989万
+$15,599/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>E | 541呎 (2房)
+$857万
+$15,848/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$2126万
+$17,624/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1379万
+$16,092/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1673万
+$18,146/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$914万
+$14,424/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$824万
+$15,212/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$2108万
+$17,497/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1372万
+$16,012/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1665万
+$18,055/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$944万
+$14,894/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>E | 541呎 (2房)
+$820万
+$15,165/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$2000万
+$16,583/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1352万
+$15,771/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1640万
+$17,785/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$896万
+$14,137/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>E | 542呎 (2房)
+$839万
+$15,472/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$1995万
+$16,540/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+$1325万
+$15,456/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 922呎 (3房)
+$1627万
+$17,645/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 634呎 (2房)
+$914万
+$14,412/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>E | 541呎 (2房)
+$822万
+$15,190/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>A | 1153呎 (4+房)
+$2236万
+$19,391/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 809呎 (3房)
+$1534万
+$18,956/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 892呎 (3房)
+$1674万
+$18,763/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 608呎 (2房)
+$1059万
+$17,414/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>E | 508呎 (2房)
+$995万
+$19,581/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1-B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>53&amp;55</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2615呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1806呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1604呎 (4+房)
+$3260万
+$20,324/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 948呎 (3房)
+$1576万
+$16,626/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1604呎 (4+房)
+$3250万
+$20,262/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 948呎 (3房)
+$2164万
+$22,830/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1557万
+$19,535/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1546万
+$20,082/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$798万
+$16,488/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$789万
+$16,262/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1557万
+$19,535/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1519万
+$19,726/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$796万
+$16,455/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$787万
+$16,231/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1542万
+$19,373/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1472万
+$19,110/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$825万
+$17,041/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$815万
+$16,808/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1538万
+$19,315/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1521万
+$19,755/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$823万
+$17,008/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$814万
+$16,775/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1533万
+$19,258/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1427万
+$18,530/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$822万
+$16,973/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$812万
+$16,742/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1528万
+$19,200/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1423万
+$18,475/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$820万
+$16,940/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$810万
+$16,709/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1524万
+$19,118/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1436万
+$18,652/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$788万
+$16,291/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$809万
+$16,674/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1514万
+$18,992/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1408万
+$18,279/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$817万
+$16,872/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$778万
+$16,037/呎
+(21年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1509万
+$18,959/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1456万
+$18,913/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$815万
+$16,839/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$776万
+$16,004/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1505万
+$18,903/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1461万
+$18,970/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$784万
+$16,194/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$775万
+$15,973/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1505万
+$18,903/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1399万
+$18,170/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$782万
+$16,161/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$773万
+$15,940/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1552万
+$19,499/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1391万
+$18,061/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$810万
+$16,738/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$801万
+$16,509/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1491万
+$18,734/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1297万
+$16,845/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$779万
+$16,097/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$799万
+$16,476/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1344万
+$16,866/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1344万
+$17,449/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$807万
+$16,671/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$798万
+$16,443/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1401万
+$17,599/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1349万
+$17,525/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$805万
+$16,636/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$796万
+$16,410/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1339万
+$16,827/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1339万
+$17,387/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$804万
+$16,605/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$794万
+$16,379/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1337万
+$16,796/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1336万
+$17,356/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$773万
+$15,969/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$793万
+$16,344/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1393万
+$17,505/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1399万
+$18,165/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$800万
+$16,539/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$791万
+$16,311/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1332万
+$16,736/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1283万
+$16,665/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$799万
+$16,504/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$790万
+$16,280/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1330万
+$16,706/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1281万
+$16,635/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$797万
+$16,471/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$788万
+$16,247/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1327万
+$16,676/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1279万
+$16,605/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$767万
+$15,841/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$786万
+$16,214/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1325万
+$16,646/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1276万
+$16,575/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$794万
+$16,405/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$785万
+$16,184/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1381万
+$17,348/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1274万
+$16,545/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$764万
+$15,777/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$755万
+$15,563/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1320万
+$16,587/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1320万
+$17,139/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$791万
+$16,341/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$782万
+$16,118/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1318万
+$16,557/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1269万
+$16,486/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$785万
+$16,211/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$776万
+$15,990/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1314万
+$16,506/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1266万
+$16,436/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$783万
+$16,180/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$746万
+$15,377/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1433万
+$18,004/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1262万
+$16,387/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$782万
+$16,147/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$744万
+$15,346/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1355万
+$17,006/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1258万
+$16,339/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$780万
+$16,114/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$743万
+$15,315/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1417万
+$17,777/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1254万
+$16,288/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$750万
+$15,498/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$741万
+$15,287/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1298万
+$16,290/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1361万
+$17,670/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$777万
+$16,050/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$740万
+$15,256/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1294万
+$16,261/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1247万
+$16,192/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$775万
+$16,017/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$766万
+$15,800/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1290万
+$16,192/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1298万
+$16,855/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$746万
+$15,405/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$765万
+$15,767/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1400万
+$17,587/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1348万
+$17,512/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$744万
+$15,374/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$735万
+$15,163/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1283万
+$16,095/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1282万
+$16,652/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$743万
+$15,343/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$734万
+$15,134/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1279万
+$16,067/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1232万
+$15,997/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$769万
+$15,890/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$760万
+$15,672/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1275万
+$15,999/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1228万
+$15,951/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$740万
+$15,281/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$731万
+$15,074/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1271万
+$15,951/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1224万
+$15,901/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$766万
+$15,826/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$757万
+$15,612/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1267万
+$15,902/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1221万
+$15,855/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$737万
+$15,221/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$728万
+$15,012/呎
+(21年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1317万
+$16,540/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1215万
+$15,775/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$733万
+$15,145/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$752万
+$15,501/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 796呎 (3房)
+$1242万
+$15,606/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1249万
+$16,221/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$749万
+$15,479/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$741万
+$15,270/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>A | 797呎 (3房)
+$1217万
+$15,275/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 770呎 (3房)
+$1169万
+$15,179/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+$707万
+$14,603/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 485呎 (2房)
+$699万
+$14,412/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>A | 754呎 (3房)
+$1480万
+$19,633/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 744呎 (3房)
+$1476万
+$19,845/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 447呎 (2房)
+$908万
+$20,309/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+$911万
+$20,389/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2-A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>58&amp;59</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 3906呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 2634呎 (4+房)
+$6868万
+$26,074/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2389呎 (4+房)
+$5510万
+$23,064/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1997呎 (4+房)
+$4340万
+$21,733/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2389呎 (4+房)
+$5438万
+$22,763/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1997呎 (4+房)
+$4330万
+$21,683/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 2389呎 (4+房)
+$5410万
+$22,645/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1997呎 (4+房)
+$4310万
+$21,582/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 2389呎 (4+房)
+$5400万
+$22,604/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1997呎 (4+房)
+$4270万
+$21,382/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 2389呎 (4+房)
+$5740万
+$24,027/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1997呎 (4+房)
+$4334万
+$21,700/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1518呎 (4+房)
+$3350万
+$22,069/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 869呎 (3房)
+$1825万
+$21,005/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1812万
+$18,032/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 642呎 (2房)
+$1075万
+$16,740/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$966万
+$17,437/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1518呎 (4+房)
+$3360万
+$22,134/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 869呎 (3房)
+$1822万
+$20,962/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1877万
+$18,675/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 642呎 (2房)
+$1073万
+$16,712/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$964万
+$17,371/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1518呎 (4+房)
+$3350万
+$22,069/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 869呎 (3房)
+$1778万
+$20,455/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1877万
+$18,675/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 642呎 (2房)
+$1073万
+$16,712/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$964万
+$17,403/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1518呎 (4+房)
+$3330万
+$21,937/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 869呎 (3房)
+$1758万
+$20,228/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1801万
+$17,923/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 642呎 (2房)
+$1060万
+$16,503/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$960万
+$17,334/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1518呎 (4+房)
+$3280万
+$21,607/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 869呎 (3房)
+$1776万
+$20,438/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1877万
+$18,675/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 642呎 (2房)
+$1098万
+$17,098/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$924万
+$16,640/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1518呎 (4+房)
+$3270万
+$21,542/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 869呎 (3房)
+$1773万
+$20,398/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1862万
+$18,525/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 642呎 (2房)
+$1046万
+$16,294/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$956万
+$17,234/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1518呎 (4+房)
+$3260万
+$21,476/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 869呎 (3房)
+$1747万
+$20,107/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1790万
+$17,816/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 642呎 (2房)
+$1044万
+$16,268/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$920万
+$16,575/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3228万
+$21,223/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1531万
+$17,663/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1769万
+$17,604/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$1034万
+$16,089/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$934万
+$16,827/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3200万
+$21,039/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1528万
+$17,629/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1766万
+$17,569/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$1033万
+$16,062/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$898万
+$16,184/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3180万
+$20,907/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1525万
+$17,593/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1829万
+$18,196/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$1060万
+$16,482/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$930万
+$16,760/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3362万
+$22,104/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1696万
+$19,559/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1759万
+$17,500/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$1058万
+$16,456/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$928万
+$16,728/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3347万
+$22,005/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1770万
+$20,420/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1759万
+$17,500/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$1020万
+$15,857/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$926万
+$16,724/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3120万
+$20,513/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1732万
+$19,971/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1752万
+$17,430/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$1006万
+$15,653/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 555呎 (2房)
+$925万
+$16,661/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3349万
+$22,018/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1513万
+$17,453/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1748万
+$17,395/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$1038万
+$16,137/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$889万
+$16,052/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1521呎 (4+房)
+$3080万
+$20,250/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 867呎 (3房)
+$1577万
+$18,185/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+$1745万
+$17,360/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 643呎 (2房)
+$998万
+$15,527/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$921万
+$16,625/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3040万
+$19,974/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 866呎 (3房)
+$1562万
+$18,040/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 1003呎 (3房)
+$1729万
+$17,240/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$1016万
+$15,749/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$912万
+$16,464/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3030万
+$19,908/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 865呎 (3房)
+$1494万
+$17,266/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 1004呎 (3房)
+$1726万
+$17,188/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$1014万
+$15,716/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$910万
+$16,431/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3070万
+$20,171/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 866呎 (3房)
+$1684万
+$19,443/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 1004呎 (3房)
+$1722万
+$17,154/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$975万
+$15,116/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$875万
+$15,800/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3030万
+$19,908/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 865呎 (3房)
+$1488万
+$17,197/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 1003呎 (3房)
+$1719万
+$17,137/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$973万
+$15,085/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$907万
+$16,394/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3050万
+$20,039/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 866呎 (3房)
+$1636万
+$18,890/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 1004呎 (3房)
+$1780万
+$17,730/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$971万
+$15,056/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$905万
+$16,332/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3040万
+$19,974/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 865呎 (3房)
+$1636万
+$18,912/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 1004呎 (3房)
+$1712万
+$17,051/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$971万
+$15,056/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$903万
+$16,329/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3030万
+$19,908/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 866呎 (3房)
+$1701万
+$19,643/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 1004呎 (3房)
+$1708万
+$17,017/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$967万
+$14,995/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$901万
+$16,297/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3020万
+$19,842/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 866呎 (3房)
+$1531万
+$17,682/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 1003呎 (3房)
+$1705万
+$17,001/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$965万
+$14,966/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$899万
+$16,264/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$3010万
+$19,777/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 865呎 (3房)
+$1602万
+$18,525/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 1004呎 (3房)
+$1702万
+$16,949/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$1000万
+$15,499/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 554呎 (2房)
+$898万
+$16,202/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 1522呎 (4+房)
+$2980万
+$19,580/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 866呎 (3房)
+$1525万
+$17,612/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 1004呎 (3房)
+$1698万
+$16,915/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 645呎 (2房)
+$998万
+$15,468/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$896万
+$16,199/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2952万
+$19,358/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1463万
+$16,938/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1854万
+$18,502/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$999万
+$15,437/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 552呎 (2房)
+$860万
+$15,578/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 1526呎 (4+房)
+$2907万
+$19,050/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1459万
+$16,887/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1920万
+$19,163/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$997万
+$15,406/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$858万
+$15,521/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2940万
+$19,279/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1455万
+$16,837/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1846万
+$18,428/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$995万
+$15,376/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$856万
+$15,488/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2940万
+$19,279/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1646万
+$19,057/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1846万
+$18,428/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$995万
+$15,376/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$909万
+$16,438/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2920万
+$19,148/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1582万
+$18,309/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1839万
+$18,354/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$991万
+$15,314/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$853万
+$15,427/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2908万
+$19,070/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1577万
+$18,253/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1836万
+$18,318/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$953万
+$14,728/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$884万
+$15,976/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2899万
+$19,012/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1437万
+$16,635/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1901万
+$18,971/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$987万
+$15,252/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 552呎 (2房)
+$882万
+$15,973/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$3100万
+$20,328/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1433万
+$16,586/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1828万
+$18,246/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$985万
+$15,223/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 552呎 (2房)
+$933万
+$16,902/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$3150万
+$20,656/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1429万
+$16,536/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1893万
+$18,895/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$983万
+$15,193/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>E | 552呎 (2房)
+$878万
+$15,909/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2870万
+$18,820/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1424万
+$16,486/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1821万
+$18,172/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$981万
+$15,162/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$897万
+$16,221/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 1526呎 (4+房)
+$2865万
+$18,773/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1554万
+$17,981/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1817万
+$18,136/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$979万
+$15,131/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$875万
+$15,817/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (4+房)
+$2870万
+$18,820/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1554万
+$17,981/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1817万
+$18,136/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$943万
+$14,581/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$841万
+$15,212/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>A | 1526呎 (4+房)
+$3494万
+$22,895/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1544万
+$17,874/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1810万
+$18,063/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$940万
+$14,524/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$871万
+$15,754/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>A | 1526呎 (4+房)
+$3483万
+$22,826/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1469万
+$17,006/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1874万
+$18,707/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$973万
+$15,040/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$869万
+$15,722/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>A | 1526呎 (4+房)
+$3466万
+$22,712/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1400万
+$16,208/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1801万
+$17,973/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$968万
+$14,966/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$865万
+$15,644/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>A | 1526呎 (4+房)
+$3414万
+$22,372/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1379万
+$15,965/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1792万
+$17,883/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$954万
+$14,740/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$852万
+$15,410/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>A | 1526呎 (4+房)
+$3346万
+$21,925/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>B | 864呎 (3房)
+$1352万
+$15,646/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>C | 1002呎 (3房)
+$1874万
+$18,707/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>D | 647呎 (2房)
+$901万
+$13,921/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$835万
+$15,101/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>A | 1459呎 (4+房)
+$2855万
+$19,571/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>B | 816呎 (3房)
+$1657万
+$20,308/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>C | 973呎 (3房)
+$1869万
+$19,212/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>D | 621呎 (2房)
+$1077万
+$17,337/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>E | 519呎 (2房)
+$998万
+$19,222/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2-B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>58&amp;59</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2333呎 (4+房)
+$6152万
+$26,369/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1500呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1870呎 (4+房)
+$4153万
+$22,207/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$3116万
+$19,375/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 958呎 (2房)
+$1690万
+$17,641/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1042呎 (2房)
+$2075万
+$19,914/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$3116万
+$19,375/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 958呎 (2房)
+$2271万
+$23,707/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 1042呎 (2房)
+$2398万
+$23,016/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$3116万
+$19,375/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 958呎 (2房)
+$2262万
+$23,613/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 1042呎 (2房)
+$2389万
+$22,925/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$3116万
+$19,375/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 958呎 (2房)
+$2253万
+$23,519/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 1042呎 (2房)
+$2039万
+$19,566/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$3115万
+$19,374/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 958呎 (2房)
+$1688万
+$17,620/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 1042呎 (2房)
+$1931万
+$18,536/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 884呎 (3房)
+$1656万
+$18,738/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1324万
+$18,601/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$826万
+$16,033/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$803万
+$16,595/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$835万
+$17,260/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$873万
+$16,894/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 884呎 (3房)
+$1653万
+$18,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 711呎 (2房)
+$1380万
+$19,408/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 516呎 (2房)
+$855万
+$16,572/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$802万
+$16,562/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$803万
+$16,599/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$905万
+$17,497/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 884呎 (3房)
+$1612万
+$18,241/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 711呎 (2房)
+$1322万
+$18,589/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 516呎 (2房)
+$822万
+$15,938/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 537呎 (2房)
+$830万
+$15,460/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$802万
+$16,566/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$905万
+$17,497/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 884呎 (3房)
+$1646万
+$18,626/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 711呎 (2房)
+$1374万
+$19,331/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$852万
+$16,538/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$828万
+$17,118/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$800万
+$16,533/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$868万
+$16,793/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 884呎 (3房)
+$1643万
+$18,589/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 711呎 (2房)
+$1314万
+$18,478/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$850万
+$16,505/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$797万
+$16,463/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$799万
+$16,500/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$899万
+$17,391/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 884呎 (3房)
+$1640万
+$18,551/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 711呎 (2房)
+$1311万
+$18,442/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$818万
+$15,874/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$795万
+$16,430/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$797万
+$16,467/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$897万
+$17,356/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 884呎 (3房)
+$1637万
+$18,515/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 711呎 (2房)
+$1309万
+$18,405/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$847万
+$16,439/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$824万
+$17,017/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$826万
+$17,056/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$863万
+$16,692/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 883呎 (3房)
+$1592万
+$18,025/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1308万
+$18,368/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$845万
+$16,406/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$792万
+$16,364/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$824万
+$17,021/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$894万
+$17,288/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 883呎 (3房)
+$1588万
+$17,989/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1305万
+$18,331/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$843万
+$16,373/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$820万
+$16,948/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$792万
+$16,370/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$860万
+$16,627/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 882呎 (3房)
+$1585万
+$17,973/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1352万
+$18,958/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 516呎 (2房)
+$842万
+$16,308/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$789万
+$16,300/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$791万
+$16,337/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$858万
+$16,594/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 883呎 (3房)
+$1652万
+$18,706/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1349万
+$18,947/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 516呎 (2房)
+$809万
+$15,684/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$817万
+$16,880/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$789万
+$16,304/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$856万
+$16,559/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 883呎 (3房)
+$1582万
+$17,916/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1300万
+$18,233/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 516呎 (2房)
+$808万
+$15,653/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$815万
+$16,847/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$788万
+$16,271/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$856万
+$16,559/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 883呎 (3房)
+$1576万
+$17,845/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1295万
+$18,185/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$806万
+$15,652/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$784万
+$16,202/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$816万
+$16,851/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$885万
+$17,116/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 883呎 (3房)
+$1632万
+$18,481/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1292万
+$18,149/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 515呎 (2房)
+$804万
+$15,621/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$783万
+$16,169/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$814万
+$16,818/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$851万
+$16,460/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 883呎 (3房)
+$1629万
+$18,445/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1338万
+$18,796/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 516呎 (2房)
+$833万
+$16,145/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$810万
+$16,746/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 484呎 (2房)
+$812万
+$16,783/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$849万
+$16,427/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1522万
+$17,276/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1254万
+$17,605/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$793万
+$15,466/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (2房)
+$807万
+$16,579/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 487呎 (2房)
+$780万
+$16,012/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$871万
+$16,913/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1576万
+$17,912/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1251万
+$17,570/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$822万
+$16,018/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (2房)
+$806万
+$16,546/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 487呎 (2房)
+$808万
+$16,583/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$838万
+$16,266/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1516万
+$17,207/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1248万
+$17,511/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$820万
+$15,986/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (2房)
+$775万
+$15,912/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$777万
+$15,981/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$836万
+$16,233/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1513万
+$17,173/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1246万
+$17,500/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$818万
+$15,953/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 486呎 (2房)
+$803万
+$16,514/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$804万
+$16,551/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$834万
+$16,200/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1510万
+$17,137/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1244万
+$17,440/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$817万
+$15,922/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 486呎 (2房)
+$801万
+$16,481/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$774万
+$15,918/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$864万
+$16,779/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1567万
+$17,784/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1244万
+$17,440/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$815万
+$15,889/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 486呎 (2房)
+$799万
+$16,449/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 487呎 (2房)
+$772万
+$15,854/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$864万
+$16,779/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1504万
+$17,070/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1285万
+$18,052/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$784万
+$15,283/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (2房)
+$798万
+$16,382/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$800万
+$16,453/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$829万
+$16,103/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1501万
+$17,036/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1236万
+$17,361/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$812万
+$15,827/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (2房)
+$796万
+$16,349/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$769万
+$15,823/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$859万
+$16,678/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 881呎 (3房)
+$1498万
+$17,001/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1234万
+$17,327/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$810万
+$15,795/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 486呎 (2房)
+$795万
+$16,350/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 487呎 (2房)
+$768万
+$15,760/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$857万
+$16,645/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1495万
+$16,988/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1231万
+$17,292/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$809万
+$15,764/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 486呎 (2房)
+$764万
+$15,724/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$795万
+$16,356/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>F | 515呎 (2房)
+$824万
+$16,008/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1483万
+$16,853/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1254万
+$17,608/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$776万
+$15,190/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$766万
+$15,693/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$796万
+$16,322/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$850万
+$16,579/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1479万
+$16,803/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1221万
+$17,126/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$775万
+$15,129/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$793万
+$16,252/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$766万
+$15,697/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$849万
+$16,544/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1474万
+$16,753/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1219万
+$17,125/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$773万
+$15,100/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$792万
+$16,221/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$793万
+$16,256/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$847万
+$16,513/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1474万
+$16,772/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1265万
+$17,771/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$801万
+$15,637/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$790万
+$16,189/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$792万
+$16,223/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$847万
+$16,513/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1465万
+$16,652/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1216万
+$17,073/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$799万
+$15,638/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$788万
+$16,154/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$790万
+$16,193/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$844万
+$16,446/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1461万
+$16,602/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1214万
+$17,048/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$798万
+$15,576/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$758万
+$15,537/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$789万
+$16,160/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$842万
+$16,413/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1457万
+$16,552/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1212万
+$17,021/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$796万
+$15,543/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$785万
+$16,090/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$787万
+$16,127/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$840万
+$16,380/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1507万
+$17,146/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1210万
+$16,996/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$794万
+$15,514/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$755万
+$15,473/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$785万
+$16,094/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$839万
+$16,347/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1502万
+$17,093/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1208万
+$16,971/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$764万
+$14,949/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$782万
+$16,027/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$784万
+$16,064/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$806万
+$15,721/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1498万
+$17,043/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1206万
+$16,945/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$762万
+$14,920/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$752万
+$15,412/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$782万
+$16,031/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$835万
+$16,283/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1439万
+$16,373/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1205万
+$16,920/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$790万
+$15,450/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$779万
+$15,961/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$752万
+$15,418/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$834万
+$16,250/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1494万
+$16,991/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1205万
+$16,896/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$788万
+$15,419/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$777万
+$15,930/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$751万
+$15,385/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$803万
+$15,659/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>A | 880呎 (3房)
+$1431万
+$16,258/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1201万
+$16,869/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$758万
+$14,830/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$776万
+$15,900/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$778万
+$15,934/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$830万
+$16,183/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1353万
+$15,396/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1245万
+$17,480/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 511呎 (2房)
+$785万
+$15,358/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$746万
+$15,291/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$776万
+$15,902/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$829万
+$16,152/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1419万
+$16,146/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1196万
+$16,794/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$752万
+$14,697/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$770万
+$15,787/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$744万
+$15,248/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$794万
+$15,487/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1459万
+$16,603/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>B | 713呎 (2房)
+$1242万
+$17,421/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$741万
+$14,477/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$731万
+$14,986/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$733万
+$15,020/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$783万
+$15,255/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>A | 879呎 (3房)
+$1370万
+$15,586/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>B | 712呎 (2房)
+$1222万
+$17,167/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$754万
+$14,723/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$717万
+$14,686/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$745万
+$15,275/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>F | 513呎 (2房)
+$796万
+$15,513/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>A | 831呎 (3房)
+$1496万
+$18,001/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>B | 676呎 (2房)
+$1496万
+$22,133/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>C | 472呎 (2房)
+$1123万
+$23,786/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$854万
+$18,900/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$856万
+$18,942/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>F | 474呎 (2房)
+$926万
+$19,546/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-将军澳-LP10.xlsx
+++ b/files/九龙-将军澳-LP10.xlsx
@@ -656,7 +656,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
